--- a/reports/scan/fs_corp_filesystem.xlsx
+++ b/reports/scan/fs_corp_filesystem.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -622,9 +622,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -699,9 +699,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -714,9 +714,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -850,49 +850,49 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -900,7 +900,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -917,62 +917,62 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1007,26 +1007,26 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1084,9 +1084,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1099,9 +1099,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -1300,74 +1300,74 @@
           <t>projects/</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1504,9 +1504,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1581,9 +1581,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1658,9 +1658,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">

--- a/reports/scan/fs_corp_filesystem.xlsx
+++ b/reports/scan/fs_corp_filesystem.xlsx
@@ -622,9 +622,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -684,74 +684,74 @@
           <t>projects/db_schema.sql</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -776,9 +776,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -840,67 +840,67 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -917,62 +917,62 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -994,67 +994,67 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1084,9 +1084,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1148,72 +1148,72 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1225,72 +1225,72 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1300,74 +1300,74 @@
           <t>projects/</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1377,74 +1377,74 @@
           <t>sensitive/security/</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1479,44 +1479,44 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1578,27 +1578,27 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1633,44 +1633,44 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1954,7 +1954,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">

--- a/reports/scan/fs_corp_filesystem.xlsx
+++ b/reports/scan/fs_corp_filesystem.xlsx
@@ -855,47 +855,47 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1171,9 +1171,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1288,9 +1288,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1360,9 +1360,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1377,9 +1377,9 @@
           <t>sensitive/security/</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>45</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1514,9 +1514,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1556,9 +1556,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
@@ -1591,14 +1591,14 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1633,9 +1633,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1668,9 +1668,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
